--- a/ParaBank Capstone – QA Documentation.xlsx
+++ b/ParaBank Capstone – QA Documentation.xlsx
@@ -8,26 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\CAPSTONE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EBB5A7-2823-40AE-BFAE-CE55EA8DF10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C51229-2476-4AFE-A87F-B5138EC20716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Plan" sheetId="1" r:id="rId1"/>
-    <sheet name="Functional_Requirements_" sheetId="2" r:id="rId2"/>
+    <sheet name="Functional_Requirements" sheetId="2" r:id="rId2"/>
     <sheet name="Test_Scenarios" sheetId="3" r:id="rId3"/>
-    <sheet name="Test_Cases_" sheetId="4" r:id="rId4"/>
+    <sheet name="Test_Cases" sheetId="4" r:id="rId4"/>
     <sheet name="RTM" sheetId="5" r:id="rId5"/>
-    <sheet name="Test_Execution_" sheetId="6" r:id="rId6"/>
+    <sheet name="Test_Execution" sheetId="6" r:id="rId6"/>
     <sheet name="Defect_Report" sheetId="7" r:id="rId7"/>
-    <sheet name="Test_Summary_Report_" sheetId="8" r:id="rId8"/>
+    <sheet name="Test_Summary_Report" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="444">
   <si>
     <t>Item</t>
   </si>
@@ -1174,12 +1174,6 @@
     <t>BUG-001</t>
   </si>
   <si>
-    <t>FAIL @ Line 26 (TC-TX-UI-02.robot)
-Step: Page Should Not Contain  'Transfer Complete!'
-BUG-001: ParaBank processes $0 transfer and shows 'Transfer Complete!'
-Expected: Zero-amount transfer should be rejected</t>
-  </si>
-  <si>
     <t>Fail</t>
   </si>
   <si>
@@ -1195,12 +1189,6 @@
     <t>BUG-002</t>
   </si>
   <si>
-    <t>FAIL @ Line 25 (TC-TX-UI-05.robot)
-Step: Page Should Not Contain  'Transfer Complete!'
-BUG-002: ParaBank processes $100,000,000 transfer and shows 'Transfer Complete!'
-Expected: Excessive-amount transfer should be rejected</t>
-  </si>
-  <si>
     <t>API Based Test Cases</t>
   </si>
   <si>
@@ -1234,12 +1222,6 @@
     <t>350ms</t>
   </si>
   <si>
-    <t>FAIL @ Line 12 (TC-API-08.robot)
-Step: Get Account Details  ${INVALID_ID}  [id=99999]
-GET /accounts/99999 → HTTP 400 raises HTTPError in RequestsLibrary
-No expected_status param set — unhandled error causes test failure</t>
-  </si>
-  <si>
     <t>Verify POST Transfer Fails for Amount Exceeding Balance</t>
   </si>
   <si>
@@ -1247,12 +1229,6 @@
   </si>
   <si>
     <t>BUG-003</t>
-  </si>
-  <si>
-    <t>FAIL @ Line 10 (TC-API-09.robot)
-Step: Should Not Be Equal As Integers  ${response.status_code}  200
-BUG-003: POST /transfer?amount=999999 returns HTTP 200
-Expected: Transfer exceeding balance should be rejected (non-200)</t>
   </si>
   <si>
     <t>Verify Destination Account Transaction History — Credit Entry</t>
@@ -1585,12 +1561,51 @@
   <si>
     <t>PARABANK CAPSTONE – TEST PLAN</t>
   </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VrSl6M9qCKTEP-kawJNPyg9qi3n_zyEt/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1fZ6vAV_JPhud_XpUUI3h3V4sM4IJ2aco/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Xx7f4qTRc14EVX_ghEQtmQNPKypNl-ST/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rIOQyatRzPhOj7E_7kflS3Vl2zr1qbfw/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ZMrelgQGDmajTo9pv1kEsKIpQwK-DaSW/view?usp=drive_link        https://drive.google.com/file/d/1XxXTHpgjDFLz9nqY31tjU0wAKKAj3nO9/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/141sDQTMEFhSz7IVHMmUq4S3mW2hVvHd0/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rCdc43pWgoQEkyGe8Aq0TGllDUp0D61C/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11l2A3m_5GllmOqQOxLcJpPE0ggdptEvt/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1kS_Sa_ibQePskaczmsQvwdxS9e8E55NS/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JRbug_bWssTRfK2CYyBDRlgCkQwLnnsD/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1LyXz0K9bUp40QaYvqaP0Q9hH2U0n8M8A?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1RVxYRLjwUWIlEemKgilXgvDU1BijWrKS/view?usp=drive_link             https://drive.google.com/drive/folders/1LyXz0K9bUp40QaYvqaP0Q9hH2U0n8M8A?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1QyvVAlSKLZfvGgtf7zgy6t45nFdii9MN/view?usp=drive_link                   https://drive.google.com/drive/folders/1LyXz0K9bUp40QaYvqaP0Q9hH2U0n8M8A?usp=drive_link</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1649,9 +1664,17 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF9C0006"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1781,10 +1804,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1829,26 +1853,39 @@
     <xf numFmtId="0" fontId="7" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2119,10 +2156,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
-        <v>434</v>
-      </c>
-      <c r="B1" s="21"/>
+      <c r="A1" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="B1" s="17"/>
     </row>
     <row r="2" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2145,7 +2182,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="73.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2153,7 +2190,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2169,7 +2206,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2185,7 +2222,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -2193,7 +2230,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2209,7 +2246,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="124.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2217,7 +2254,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2225,7 +2262,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -2250,14 +2287,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2484,16 +2521,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
     </row>
     <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2753,15 +2790,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2796,15 +2833,15 @@
       <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="21"/>
     </row>
     <row r="5" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
@@ -3046,15 +3083,15 @@
       <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="21"/>
     </row>
     <row r="17" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
@@ -3296,15 +3333,15 @@
       <c r="G27" s="6"/>
     </row>
     <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="19"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="21"/>
     </row>
     <row r="29" spans="1:7" ht="139.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
@@ -3377,13 +3414,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>255</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
     </row>
     <row r="2" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -3578,74 +3615,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>418</v>
-      </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="B3" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
     </row>
     <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="B6" s="23" t="s">
-        <v>426</v>
-      </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
+      <c r="B6" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
     </row>
     <row r="8" spans="1:6" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
@@ -3656,14 +3693,14 @@
       <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="21"/>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -3698,7 +3735,9 @@
       <c r="D11" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="E11" s="13"/>
+      <c r="E11" s="22" t="s">
+        <v>435</v>
+      </c>
       <c r="F11" s="14" t="s">
         <v>302</v>
       </c>
@@ -3716,7 +3755,9 @@
       <c r="D12" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E12" s="15"/>
+      <c r="E12" s="23" t="s">
+        <v>431</v>
+      </c>
       <c r="F12" s="14" t="s">
         <v>302</v>
       </c>
@@ -3734,7 +3775,9 @@
       <c r="D13" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="E13" s="13"/>
+      <c r="E13" s="13" t="s">
+        <v>432</v>
+      </c>
       <c r="F13" s="14" t="s">
         <v>302</v>
       </c>
@@ -3752,7 +3795,9 @@
       <c r="D14" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E14" s="15"/>
+      <c r="E14" s="15" t="s">
+        <v>433</v>
+      </c>
       <c r="F14" s="14" t="s">
         <v>302</v>
       </c>
@@ -3770,7 +3815,9 @@
       <c r="D15" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="E15" s="13"/>
+      <c r="E15" s="13" t="s">
+        <v>434</v>
+      </c>
       <c r="F15" s="14" t="s">
         <v>302</v>
       </c>
@@ -3788,12 +3835,14 @@
       <c r="D16" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E16" s="15"/>
+      <c r="E16" s="15" t="s">
+        <v>436</v>
+      </c>
       <c r="F16" s="14" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>163</v>
       </c>
@@ -3806,11 +3855,11 @@
       <c r="D17" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="24" t="s">
+        <v>437</v>
+      </c>
+      <c r="F17" s="12" t="s">
         <v>314</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3821,12 +3870,14 @@
         <v>169</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E18" s="15"/>
+      <c r="E18" s="15" t="s">
+        <v>438</v>
+      </c>
       <c r="F18" s="14" t="s">
         <v>302</v>
       </c>
@@ -3844,29 +3895,31 @@
       <c r="D19" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="E19" s="13"/>
+      <c r="E19" s="22" t="s">
+        <v>439</v>
+      </c>
       <c r="F19" s="14" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>178</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="D20" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>320</v>
+      <c r="E20" s="25" t="s">
+        <v>440</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3878,14 +3931,14 @@
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="19"/>
+      <c r="A22" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="21"/>
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
@@ -3915,12 +3968,14 @@
         <v>185</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="E24" s="13"/>
+      <c r="E24" s="13" t="s">
+        <v>441</v>
+      </c>
       <c r="F24" s="14" t="s">
         <v>302</v>
       </c>
@@ -3933,12 +3988,14 @@
         <v>191</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E25" s="15"/>
+      <c r="E25" s="15" t="s">
+        <v>441</v>
+      </c>
       <c r="F25" s="14" t="s">
         <v>302</v>
       </c>
@@ -3951,12 +4008,14 @@
         <v>197</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="E26" s="13"/>
+      <c r="E26" s="13" t="s">
+        <v>441</v>
+      </c>
       <c r="F26" s="14" t="s">
         <v>302</v>
       </c>
@@ -3969,12 +4028,14 @@
         <v>203</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E27" s="15"/>
+      <c r="E27" s="15" t="s">
+        <v>441</v>
+      </c>
       <c r="F27" s="14" t="s">
         <v>302</v>
       </c>
@@ -3987,12 +4048,14 @@
         <v>209</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="E28" s="13"/>
+      <c r="E28" s="13" t="s">
+        <v>441</v>
+      </c>
       <c r="F28" s="14" t="s">
         <v>302</v>
       </c>
@@ -4002,15 +4065,17 @@
         <v>214</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E29" s="15"/>
+      <c r="E29" s="15" t="s">
+        <v>441</v>
+      </c>
       <c r="F29" s="14" t="s">
         <v>302</v>
       </c>
@@ -4020,20 +4085,22 @@
         <v>220</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="E30" s="13"/>
+      <c r="E30" s="13" t="s">
+        <v>441</v>
+      </c>
       <c r="F30" s="14" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>225</v>
       </c>
@@ -4041,36 +4108,36 @@
         <v>226</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E31" s="17" t="s">
-        <v>332</v>
+      <c r="E31" s="25" t="s">
+        <v>441</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>231</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>336</v>
+        <v>332</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>441</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -4078,15 +4145,17 @@
         <v>237</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E33" s="15"/>
+      <c r="E33" s="15" t="s">
+        <v>441</v>
+      </c>
       <c r="F33" s="14" t="s">
         <v>302</v>
       </c>
@@ -4100,14 +4169,14 @@
       <c r="F34" s="6"/>
     </row>
     <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="19"/>
+      <c r="A35" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="21"/>
     </row>
     <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
@@ -4137,12 +4206,14 @@
         <v>244</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="E37" s="13"/>
+      <c r="E37" s="26" t="s">
+        <v>442</v>
+      </c>
       <c r="F37" s="14" t="s">
         <v>302</v>
       </c>
@@ -4155,19 +4226,20 @@
         <v>250</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E38" s="15"/>
+      <c r="E38" s="27" t="s">
+        <v>443</v>
+      </c>
       <c r="F38" s="14" t="s">
         <v>302</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A9:F9"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="B4:F4"/>
@@ -4176,7 +4248,17 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E11" r:id="rId1" display="https://drive.google.com/file/d/1ZMrelgQGDmajTo9pv1kEsKIpQwK-DaSW/view?usp=drive_link   " xr:uid="{B8305445-A73C-4E18-8D88-F62E5501B5DE}"/>
+    <hyperlink ref="E12" r:id="rId2" xr:uid="{CA63BBB2-40F5-4693-B712-E1286D355906}"/>
+    <hyperlink ref="E17" r:id="rId3" xr:uid="{079D51A2-5C9C-4B95-AD56-0B0F025F271B}"/>
+    <hyperlink ref="E19" r:id="rId4" xr:uid="{D483BB79-CBCA-418D-9E32-4D2F87D0AE5F}"/>
+    <hyperlink ref="E20" r:id="rId5" xr:uid="{0B65349D-22A3-48F1-9842-340437036002}"/>
+    <hyperlink ref="E31" r:id="rId6" xr:uid="{2D91C4DA-E3EA-4CCE-B644-A15A2E68AB41}"/>
+    <hyperlink ref="E32" r:id="rId7" xr:uid="{74120D4E-9079-4BC1-A512-B73EF4699997}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -4198,18 +4280,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
-        <v>341</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
+      <c r="A1" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -4222,19 +4304,19 @@
         <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>74</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>24</v>
@@ -4254,16 +4336,16 @@
         <v>63</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>62</v>
@@ -4272,12 +4354,12 @@
         <v>62</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>178</v>
@@ -4286,16 +4368,16 @@
         <v>63</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>30</v>
@@ -4304,12 +4386,12 @@
         <v>30</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>231</v>
@@ -4318,16 +4400,16 @@
         <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>30</v>
@@ -4336,7 +4418,7 @@
         <v>30</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -4358,14 +4440,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="B1" s="21"/>
+      <c r="A1" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="B1" s="17"/>
     </row>
     <row r="2" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>288</v>
@@ -4373,26 +4455,26 @@
     </row>
     <row r="3" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4400,14 +4482,14 @@
       <c r="B6" s="6"/>
     </row>
     <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
-        <v>366</v>
-      </c>
-      <c r="B7" s="19"/>
+      <c r="A7" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B8" s="3">
         <v>22</v>
@@ -4415,7 +4497,7 @@
     </row>
     <row r="9" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B9" s="5">
         <v>22</v>
@@ -4423,7 +4505,7 @@
     </row>
     <row r="10" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B10" s="3">
         <v>18</v>
@@ -4431,7 +4513,7 @@
     </row>
     <row r="11" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B11" s="5">
         <v>4</v>
@@ -4439,7 +4521,7 @@
     </row>
     <row r="12" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B12" s="3">
         <v>0</v>
@@ -4447,18 +4529,18 @@
     </row>
     <row r="13" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4466,41 +4548,41 @@
       <c r="B15" s="6"/>
     </row>
     <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
-        <v>375</v>
-      </c>
-      <c r="B16" s="19"/>
+      <c r="A16" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="B16" s="21"/>
     </row>
     <row r="17" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4508,17 +4590,17 @@
       <c r="B21" s="6"/>
     </row>
     <row r="22" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
-        <v>383</v>
-      </c>
-      <c r="B22" s="19"/>
+      <c r="A22" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="B22" s="21"/>
     </row>
     <row r="23" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4526,15 +4608,15 @@
         <v>259</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4542,14 +4624,14 @@
       <c r="B26" s="6"/>
     </row>
     <row r="27" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="B27" s="19"/>
+      <c r="A27" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B27" s="21"/>
     </row>
     <row r="28" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B28" s="3">
         <v>3</v>
@@ -4557,7 +4639,7 @@
     </row>
     <row r="29" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B29" s="5">
         <v>0</v>
@@ -4565,23 +4647,23 @@
     </row>
     <row r="30" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B32" s="3">
         <v>0</v>
@@ -4592,41 +4674,41 @@
       <c r="B33" s="6"/>
     </row>
     <row r="34" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="18" t="s">
-        <v>394</v>
-      </c>
-      <c r="B34" s="19"/>
+      <c r="A34" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="B34" s="21"/>
     </row>
     <row r="35" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4634,57 +4716,57 @@
       <c r="B39" s="6"/>
     </row>
     <row r="40" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="B40" s="19"/>
+      <c r="A40" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="B40" s="21"/>
     </row>
     <row r="41" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4692,25 +4774,25 @@
       <c r="B47" s="6"/>
     </row>
     <row r="48" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="B48" s="19"/>
+      <c r="A48" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="B48" s="21"/>
     </row>
     <row r="49" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>299</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>

--- a/ParaBank Capstone – QA Documentation.xlsx
+++ b/ParaBank Capstone – QA Documentation.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C51229-2476-4AFE-A87F-B5138EC20716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Plan" sheetId="1" r:id="rId1"/>
@@ -1853,18 +1853,6 @@
     <xf numFmtId="0" fontId="7" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1882,6 +1870,18 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2156,10 +2156,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="27" t="s">
         <v>430</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="26"/>
     </row>
     <row r="2" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2287,14 +2287,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2521,16 +2521,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2790,15 +2790,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2833,15 +2833,15 @@
       <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="21"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="24"/>
     </row>
     <row r="5" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
@@ -3083,15 +3083,15 @@
       <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="21"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="24"/>
     </row>
     <row r="17" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
@@ -3333,15 +3333,15 @@
       <c r="G27" s="6"/>
     </row>
     <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="22" t="s">
         <v>242</v>
       </c>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="21"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="24"/>
     </row>
     <row r="29" spans="1:7" ht="139.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
@@ -3414,13 +3414,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -3615,74 +3615,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="27" t="s">
         <v>286</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="25" t="s">
         <v>288</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="25" t="s">
         <v>414</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="25" t="s">
         <v>291</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
     </row>
     <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="25" t="s">
         <v>422</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
     </row>
     <row r="8" spans="1:6" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
@@ -3693,14 +3693,14 @@
       <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="22" t="s">
         <v>295</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="21"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="24"/>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -3735,7 +3735,7 @@
       <c r="D11" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="16" t="s">
         <v>435</v>
       </c>
       <c r="F11" s="14" t="s">
@@ -3755,7 +3755,7 @@
       <c r="D12" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="17" t="s">
         <v>431</v>
       </c>
       <c r="F12" s="14" t="s">
@@ -3855,7 +3855,7 @@
       <c r="D17" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="18" t="s">
         <v>437</v>
       </c>
       <c r="F17" s="12" t="s">
@@ -3895,7 +3895,7 @@
       <c r="D19" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="16" t="s">
         <v>439</v>
       </c>
       <c r="F19" s="14" t="s">
@@ -3915,7 +3915,7 @@
       <c r="D20" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="E20" s="19" t="s">
         <v>440</v>
       </c>
       <c r="F20" s="12" t="s">
@@ -3931,14 +3931,14 @@
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="22" t="s">
         <v>319</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="21"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="24"/>
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
@@ -4113,7 +4113,7 @@
       <c r="D31" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E31" s="25" t="s">
+      <c r="E31" s="19" t="s">
         <v>441</v>
       </c>
       <c r="F31" s="12" t="s">
@@ -4133,7 +4133,7 @@
       <c r="D32" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="18" t="s">
         <v>441</v>
       </c>
       <c r="F32" s="12" t="s">
@@ -4169,14 +4169,14 @@
       <c r="F34" s="6"/>
     </row>
     <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="22" t="s">
         <v>334</v>
       </c>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="21"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="24"/>
     </row>
     <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
@@ -4211,7 +4211,7 @@
       <c r="D37" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="E37" s="26" t="s">
+      <c r="E37" s="20" t="s">
         <v>442</v>
       </c>
       <c r="F37" s="14" t="s">
@@ -4231,7 +4231,7 @@
       <c r="D38" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E38" s="27" t="s">
+      <c r="E38" s="21" t="s">
         <v>443</v>
       </c>
       <c r="F38" s="14" t="s">
@@ -4240,15 +4240,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A9:F9"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E11" r:id="rId1" display="https://drive.google.com/file/d/1ZMrelgQGDmajTo9pv1kEsKIpQwK-DaSW/view?usp=drive_link   " xr:uid="{B8305445-A73C-4E18-8D88-F62E5501B5DE}"/>
@@ -4280,18 +4280,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="27" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -4440,10 +4440,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="27" t="s">
         <v>355</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="26"/>
     </row>
     <row r="2" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -4482,10 +4482,10 @@
       <c r="B6" s="6"/>
     </row>
     <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="22" t="s">
         <v>362</v>
       </c>
-      <c r="B7" s="21"/>
+      <c r="B7" s="24"/>
     </row>
     <row r="8" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -4548,10 +4548,10 @@
       <c r="B15" s="6"/>
     </row>
     <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="22" t="s">
         <v>371</v>
       </c>
-      <c r="B16" s="21"/>
+      <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
@@ -4590,10 +4590,10 @@
       <c r="B21" s="6"/>
     </row>
     <row r="22" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="22" t="s">
         <v>379</v>
       </c>
-      <c r="B22" s="21"/>
+      <c r="B22" s="24"/>
     </row>
     <row r="23" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
@@ -4624,10 +4624,10 @@
       <c r="B26" s="6"/>
     </row>
     <row r="27" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="22" t="s">
         <v>382</v>
       </c>
-      <c r="B27" s="21"/>
+      <c r="B27" s="24"/>
     </row>
     <row r="28" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
@@ -4674,10 +4674,10 @@
       <c r="B33" s="6"/>
     </row>
     <row r="34" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="19" t="s">
+      <c r="A34" s="22" t="s">
         <v>390</v>
       </c>
-      <c r="B34" s="21"/>
+      <c r="B34" s="24"/>
     </row>
     <row r="35" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
@@ -4716,10 +4716,10 @@
       <c r="B39" s="6"/>
     </row>
     <row r="40" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="19" t="s">
+      <c r="A40" s="22" t="s">
         <v>398</v>
       </c>
-      <c r="B40" s="21"/>
+      <c r="B40" s="24"/>
     </row>
     <row r="41" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
@@ -4774,10 +4774,10 @@
       <c r="B47" s="6"/>
     </row>
     <row r="48" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="19" t="s">
+      <c r="A48" s="22" t="s">
         <v>411</v>
       </c>
-      <c r="B48" s="21"/>
+      <c r="B48" s="24"/>
     </row>
     <row r="49" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">

--- a/ParaBank Capstone – QA Documentation.xlsx
+++ b/ParaBank Capstone – QA Documentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\CAPSTONE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C51229-2476-4AFE-A87F-B5138EC20716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95CD736-B767-4D30-90C5-32FE01807F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Plan" sheetId="1" r:id="rId1"/>
@@ -61,13 +61,6 @@
     <t>Test Environment</t>
   </si>
   <si>
-    <t>• AUT: https://parabank.parasoft.com
-• Browser: Chrome (SeleniumLibrary)
-• Framework: Robot Framework 7+ | Python 3.14
-• Libraries: SeleniumLibrary, RequestsLibrary, DataDriver
-• Runner: Windows 10/11 &amp; GitHub Actions CI pipeline</t>
-  </si>
-  <si>
     <t>Entry Criteria</t>
   </si>
   <si>
@@ -1513,20 +1506,10 @@
     <t>Total: 22  |  Pass: 18  |  Fail: 4  |  Pass Rate: 81.8%</t>
   </si>
   <si>
-    <t>• AUT is online and Swagger API docs are reachable.
-• Robot Framework, SeleniumLibrary, RequestsLibrary, and DataDriver are installed.
-• Environment variables (CUSTOMER_ID, ACCOUNT_ID, ACCOUNT_ID_2, INVALID_ID) are configured.</t>
-  </si>
-  <si>
     <t>• All 22 test cases fully executed and logged.
 • Pass rate ≥ 70% (excluding documented application bugs).
 • All defects logged in Defect Report sheet.
 • RTM confirms full coverage of all functional requirements.</t>
-  </si>
-  <si>
-    <t>• Master QA Workbook: Plan, Requirements, Scenarios, Cases, RTM, Execution Log, Defects, Summary.
-• Robot Framework suites: UI, API, E2E, Negative.
-• Automation Logs: log.html, report.html, Allure report dashboards.</t>
   </si>
   <si>
     <t>FR-01: Create new account via UI
@@ -1540,19 +1523,6 @@
 FR-09: Validate negative / boundary scenarios</t>
   </si>
   <si>
-    <t>• POM: home_page.robot, open_new_account_page.robot, transfer_funds_page.robot.
-• API Library: RequestsLibrary via common_keywords.robot and api_keywords.robot.
-• Parallel Sharding: Pabot across 4 parallel processes with clean browser contexts.
-• Retries: 1 retry on failure; Smart Wait keywords instead of hard Sleeps.</t>
-  </si>
-  <si>
-    <t>In-Scope:
-• UI: Account creation, navigation, and fund transfer fields via SeleniumLibrary.
-• API: Account retrieval (GET) and transfer requests (POST).
-• E2E: UI-driven transactions validated against API ledger.
-• Negative/Boundary: Zero, blank, alphabetic, and overdraft amount inputs.</t>
-  </si>
-  <si>
     <t>• Validate account opening workflows and fund transfer screens via Selenium/Browser Library UI automation.
 • Verify REST API response structures, status codes, and data types (id, customerId, type, balance).
 • Ensure financial integrity (balance deltas and ledger entries) across UI and API transactions.
@@ -1599,6 +1569,34 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1QyvVAlSKLZfvGgtf7zgy6t45nFdii9MN/view?usp=drive_link                   https://drive.google.com/drive/folders/1LyXz0K9bUp40QaYvqaP0Q9hH2U0n8M8A?usp=drive_link</t>
+  </si>
+  <si>
+    <t>• UI: Account creation, navigation, and fund transfer fields via SeleniumLibrary.
+• API: Account retrieval (GET) and transfer requests (POST).
+• E2E: UI-driven transactions validated against API ledger.
+• Negative/Boundary: Zero, blank, alphabetic, and overdraft amount inputs.</t>
+  </si>
+  <si>
+    <t>• AUT: https://parabank.parasoft.com
+• Browser: Chrome (SeleniumLibrary)
+• Framework: Robot Framework 7+ | Python 3.14
+• Libraries: SeleniumLibrary, RequestsLibrary, DataDriver
+• Runner: Windows 10/11 &amp; GitHub Actions CI freestyle</t>
+  </si>
+  <si>
+    <t>• POM: home_page.robot, open_new_account_page.robot, transfer_funds_page.robot.
+• API Library: RequestsLibrary via api_keywords.robot.
+• Parallel Sharding: Pabot across 4 parallel processes with clean browser contexts.</t>
+  </si>
+  <si>
+    <t>• QA Documentation: Plan, Requirements, Scenarios, Cases, RTM, Execution Log, Defects, Summary.
+• Robot Framework suites: UI, API, E2E, Negative.
+• Automation Logs: log.html, report.html, Allure report dashboards.</t>
+  </si>
+  <si>
+    <t>• AUT is online and Swagger API docs are reachable.
+• Robot Framework, SeleniumLibrary, RequestsLibrary, and DataDriver are installed.
+• Variables (CUSTOMER_ID, ACCOUNT_ID, ACCOUNT_ID_2, INVALID_ID) are configured.</t>
   </si>
 </sst>
 </file>
@@ -1871,6 +1869,10 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1878,10 +1880,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2156,10 +2154,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>430</v>
-      </c>
-      <c r="B1" s="26"/>
+      <c r="A1" s="22" t="s">
+        <v>425</v>
+      </c>
+      <c r="B1" s="23"/>
     </row>
     <row r="2" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2182,7 +2180,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="73.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2190,7 +2188,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2201,12 +2199,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2214,55 +2212,55 @@
         <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>10</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="124.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -2287,213 +2285,213 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
+      <c r="A1" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="2" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>35</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>44</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2521,249 +2519,249 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="A1" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="F4" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>98</v>
-      </c>
       <c r="H6" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>109</v>
-      </c>
       <c r="G8" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="H9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="H10" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2790,37 +2788,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="A1" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2833,244 +2831,244 @@
       <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="24"/>
+      <c r="A4" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>138</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>172</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="G13" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="178.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>181</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3083,244 +3081,244 @@
       <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="24"/>
+      <c r="A16" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="26"/>
     </row>
     <row r="17" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="F22" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="G22" s="5" t="s">
         <v>218</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="G24" s="5" t="s">
         <v>229</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>240</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3333,60 +3331,60 @@
       <c r="G27" s="6"/>
     </row>
     <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="24"/>
+      <c r="A28" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="26"/>
     </row>
     <row r="29" spans="1:7" ht="139.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="160.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="E30" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="F30" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="G30" s="5" t="s">
         <v>253</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -3414,182 +3412,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>255</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
+      <c r="A1" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
     </row>
     <row r="2" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>266</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>270</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>276</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>278</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>281</v>
-      </c>
       <c r="E10" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -3615,74 +3613,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>286</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
+      <c r="A1" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B2" s="27" t="s">
         <v>287</v>
       </c>
-      <c r="B2" s="25" t="s">
-        <v>288</v>
-      </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>414</v>
-      </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
+        <v>288</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="B4" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="B4" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="B5" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="B5" s="25" t="s">
-        <v>293</v>
-      </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
     </row>
     <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>422</v>
-      </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
+        <v>293</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
     </row>
     <row r="8" spans="1:6" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
@@ -3693,233 +3691,233 @@
       <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
-        <v>295</v>
-      </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="24"/>
+      <c r="A9" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="26"/>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="C10" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>129</v>
-      </c>
       <c r="C11" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="F11" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>435</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B12" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>304</v>
-      </c>
       <c r="D12" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="F12" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>431</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>141</v>
-      </c>
       <c r="C13" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="F13" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>432</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B14" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>307</v>
-      </c>
       <c r="D14" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="F14" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>433</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>152</v>
-      </c>
       <c r="C15" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D15" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="F15" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>434</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B16" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>310</v>
-      </c>
       <c r="D16" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="F16" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="D17" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="F17" s="12" t="s">
         <v>313</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>437</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>169</v>
-      </c>
       <c r="C18" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D18" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="F18" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>175</v>
-      </c>
       <c r="C19" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D19" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="F19" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>439</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="D20" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>318</v>
-      </c>
       <c r="E20" s="19" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3931,233 +3929,233 @@
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="22" t="s">
-        <v>319</v>
-      </c>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="24"/>
+      <c r="A22" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="26"/>
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="C23" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>185</v>
-      </c>
       <c r="C24" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D24" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="F24" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="B25" s="11" t="s">
-        <v>191</v>
-      </c>
       <c r="C25" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D25" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="F25" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>197</v>
-      </c>
       <c r="C26" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D26" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="F26" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="F26" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="B27" s="11" t="s">
-        <v>203</v>
-      </c>
       <c r="C27" s="11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D27" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="F27" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B28" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>209</v>
-      </c>
       <c r="C28" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D28" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="F28" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B29" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="C29" s="11" t="s">
-        <v>326</v>
-      </c>
       <c r="D29" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="F29" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B30" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>328</v>
-      </c>
       <c r="D30" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="F30" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="B31" s="11" t="s">
-        <v>226</v>
-      </c>
       <c r="C31" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B32" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="D32" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="D32" s="9" t="s">
-        <v>332</v>
-      </c>
       <c r="E32" s="18" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D33" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="F33" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4169,86 +4167,86 @@
       <c r="F34" s="6"/>
     </row>
     <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="24"/>
+      <c r="A35" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="26"/>
     </row>
     <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="C36" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="B37" s="9" t="s">
-        <v>244</v>
-      </c>
       <c r="C37" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D37" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="F37" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>442</v>
-      </c>
-      <c r="F37" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="B38" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="B38" s="11" t="s">
-        <v>250</v>
-      </c>
       <c r="C38" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D38" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="F38" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="E38" s="21" t="s">
-        <v>443</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>302</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E11" r:id="rId1" display="https://drive.google.com/file/d/1ZMrelgQGDmajTo9pv1kEsKIpQwK-DaSW/view?usp=drive_link   " xr:uid="{B8305445-A73C-4E18-8D88-F62E5501B5DE}"/>
@@ -4280,145 +4278,145 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>337</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="A1" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>350</v>
-      </c>
       <c r="H4" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>354</v>
-      </c>
       <c r="H5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -4440,41 +4438,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>355</v>
-      </c>
-      <c r="B1" s="26"/>
+      <c r="A1" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="B1" s="23"/>
     </row>
     <row r="2" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>360</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4482,14 +4480,14 @@
       <c r="B6" s="6"/>
     </row>
     <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="B7" s="24"/>
+      <c r="A7" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="B7" s="26"/>
     </row>
     <row r="8" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B8" s="3">
         <v>22</v>
@@ -4497,7 +4495,7 @@
     </row>
     <row r="9" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B9" s="5">
         <v>22</v>
@@ -4505,7 +4503,7 @@
     </row>
     <row r="10" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B10" s="3">
         <v>18</v>
@@ -4513,7 +4511,7 @@
     </row>
     <row r="11" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B11" s="5">
         <v>4</v>
@@ -4521,7 +4519,7 @@
     </row>
     <row r="12" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B12" s="3">
         <v>0</v>
@@ -4529,18 +4527,18 @@
     </row>
     <row r="13" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>369</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4548,41 +4546,41 @@
       <c r="B15" s="6"/>
     </row>
     <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
-        <v>371</v>
-      </c>
-      <c r="B16" s="24"/>
+      <c r="A16" s="24" t="s">
+        <v>370</v>
+      </c>
+      <c r="B16" s="26"/>
     </row>
     <row r="17" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>372</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>374</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>376</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4590,33 +4588,33 @@
       <c r="B21" s="6"/>
     </row>
     <row r="22" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="22" t="s">
-        <v>379</v>
-      </c>
-      <c r="B22" s="24"/>
+      <c r="A22" s="24" t="s">
+        <v>378</v>
+      </c>
+      <c r="B22" s="26"/>
     </row>
     <row r="23" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4624,14 +4622,14 @@
       <c r="B26" s="6"/>
     </row>
     <row r="27" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="22" t="s">
-        <v>382</v>
-      </c>
-      <c r="B27" s="24"/>
+      <c r="A27" s="24" t="s">
+        <v>381</v>
+      </c>
+      <c r="B27" s="26"/>
     </row>
     <row r="28" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B28" s="3">
         <v>3</v>
@@ -4639,7 +4637,7 @@
     </row>
     <row r="29" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B29" s="5">
         <v>0</v>
@@ -4647,23 +4645,23 @@
     </row>
     <row r="30" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>385</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>387</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B32" s="3">
         <v>0</v>
@@ -4674,41 +4672,41 @@
       <c r="B33" s="6"/>
     </row>
     <row r="34" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="B34" s="24"/>
+      <c r="A34" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="B34" s="26"/>
     </row>
     <row r="35" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>391</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>393</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>395</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4716,57 +4714,57 @@
       <c r="B39" s="6"/>
     </row>
     <row r="40" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="22" t="s">
-        <v>398</v>
-      </c>
-      <c r="B40" s="24"/>
+      <c r="A40" s="24" t="s">
+        <v>397</v>
+      </c>
+      <c r="B40" s="26"/>
     </row>
     <row r="41" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>401</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>403</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>405</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>407</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>409</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4774,25 +4772,25 @@
       <c r="B47" s="6"/>
     </row>
     <row r="48" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="22" t="s">
-        <v>411</v>
-      </c>
-      <c r="B48" s="24"/>
+      <c r="A48" s="24" t="s">
+        <v>410</v>
+      </c>
+      <c r="B48" s="26"/>
     </row>
     <row r="49" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
